--- a/test_data/mercury_my_hand.xlsx
+++ b/test_data/mercury_my_hand.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27948" windowHeight="12300" firstSheet="14" activeTab="18"/>
+    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="24" activeTab="27"/>
   </bookViews>
   <sheets>
     <sheet name="get_hand_firmware_major_version" sheetId="1" r:id="rId1"/>
@@ -34,6 +34,7 @@
     <sheet name="set_hand_gripper_pose" sheetId="25" r:id="rId25"/>
     <sheet name="set_hand_gripper_speed" sheetId="26" r:id="rId26"/>
     <sheet name="set_hand_gripper_torque" sheetId="27" r:id="rId27"/>
+    <sheet name="get_hand_gripper_angles" sheetId="28" r:id="rId28"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -53,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="861" uniqueCount="268">
   <si>
     <t>ID</t>
   </si>
@@ -848,6 +849,15 @@
   </si>
   <si>
     <t>设置6关节torque值（超限）</t>
+  </si>
+  <si>
+    <t>正确获取全关节角度</t>
+  </si>
+  <si>
+    <t>[0,0,0,0,0,0]</t>
+  </si>
+  <si>
+    <t>[30,30,30,30,30,30]</t>
   </si>
 </sst>
 </file>
@@ -6217,6 +6227,104 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="3" width="19.3333333333333" style="1" customWidth="1"/>
+    <col min="4" max="4" width="25.7777777777778" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.3333333333333" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="28.8" spans="1:6">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="28.8" spans="1:6">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:6">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>

--- a/test_data/mercury_my_hand.xlsx
+++ b/test_data/mercury_my_hand.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="24" activeTab="27"/>
+    <workbookView windowWidth="27948" windowHeight="12300" firstSheet="18" activeTab="18"/>
   </bookViews>
   <sheets>
     <sheet name="get_hand_firmware_major_version" sheetId="1" r:id="rId1"/>

--- a/test_data/mercury_my_hand.xlsx
+++ b/test_data/mercury_my_hand.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27948" windowHeight="12300" firstSheet="18" activeTab="18"/>
+    <workbookView windowWidth="27948" windowHeight="12300" firstSheet="3" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="get_hand_firmware_major_version" sheetId="1" r:id="rId1"/>
     <sheet name="get_hand_firmware_minor_version" sheetId="2" r:id="rId2"/>
     <sheet name="get_hand_gripper_angle" sheetId="3" r:id="rId3"/>
     <sheet name="get_hand_gripper_clockwise" sheetId="4" r:id="rId4"/>
-    <sheet name="get_hand_gripper_cw" sheetId="5" r:id="rId5"/>
+    <sheet name="get_hand_gripper_cww" sheetId="5" r:id="rId5"/>
     <sheet name="get_hand_gripper_d" sheetId="6" r:id="rId6"/>
     <sheet name="get_hand_gripper_i" sheetId="7" r:id="rId7"/>
     <sheet name="get_hand_gripper_id" sheetId="8" r:id="rId8"/>

--- a/test_data/mercury_my_hand.xlsx
+++ b/test_data/mercury_my_hand.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27948" windowHeight="12300" firstSheet="3" activeTab="3"/>
+    <workbookView windowWidth="27948" windowHeight="12300" firstSheet="16" activeTab="16"/>
   </bookViews>
   <sheets>
     <sheet name="get_hand_firmware_major_version" sheetId="1" r:id="rId1"/>

--- a/test_data/mercury_my_hand.xlsx
+++ b/test_data/mercury_my_hand.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27948" windowHeight="12300" firstSheet="16" activeTab="16"/>
+    <workbookView windowWidth="24750" windowHeight="11870" firstSheet="15" activeTab="18"/>
   </bookViews>
   <sheets>
     <sheet name="get_hand_firmware_major_version" sheetId="1" r:id="rId1"/>
@@ -1792,9 +1792,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="5" width="19.3333333333333" style="1" customWidth="1"/>
+    <col min="1" max="5" width="19.3363636363636" style="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1815,7 +1815,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="28.8" spans="1:5">
+    <row r="2" s="1" customFormat="1" ht="28" spans="1:5">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1840,10 +1840,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="5" width="19.3333333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.2222222222222" style="1" customWidth="1"/>
+    <col min="1" max="5" width="19.3363636363636" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.2181818181818" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -2031,10 +2031,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="5" width="19.3333333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="17.4444444444444" style="1" customWidth="1"/>
+    <col min="1" max="5" width="19.3363636363636" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.4454545454545" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -2075,7 +2075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="3" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -2092,7 +2092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="43.2" spans="1:6">
+    <row r="4" s="1" customFormat="1" ht="42" spans="1:6">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -2109,7 +2109,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="43.2" spans="1:6">
+    <row r="5" s="1" customFormat="1" ht="42" spans="1:6">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -2136,10 +2136,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="5" width="19.3333333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.2222222222222" style="1" customWidth="1"/>
+    <col min="1" max="5" width="19.3363636363636" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.2181818181818" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -2327,10 +2327,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="6" width="19.3333333333333" style="1" customWidth="1"/>
-    <col min="7" max="7" width="16.2222222222222" style="1" customWidth="1"/>
+    <col min="1" max="6" width="19.3363636363636" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.2181818181818" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -2546,12 +2546,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="3" width="19.3333333333333" style="1" customWidth="1"/>
-    <col min="4" max="4" width="24.1111111111111" style="1" customWidth="1"/>
-    <col min="5" max="6" width="19.3333333333333" style="1" customWidth="1"/>
-    <col min="7" max="7" width="16.2222222222222" style="1" customWidth="1"/>
+    <col min="1" max="3" width="19.3363636363636" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.1090909090909" style="1" customWidth="1"/>
+    <col min="5" max="6" width="19.3363636363636" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.2181818181818" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -2674,10 +2674,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="5" width="19.3333333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.2222222222222" style="1" customWidth="1"/>
+    <col min="1" max="5" width="19.3363636363636" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.2181818181818" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -2838,7 +2838,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="9" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -2865,10 +2865,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="6" width="19.3333333333333" style="1" customWidth="1"/>
-    <col min="7" max="7" width="16.2222222222222" style="1" customWidth="1"/>
+    <col min="1" max="6" width="19.3363636363636" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.2181818181818" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -3093,7 +3093,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="11" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -3113,7 +3113,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="12" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -3133,7 +3133,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="13" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -3153,7 +3153,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="14" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -3173,7 +3173,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="15" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -3203,10 +3203,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="6" width="19.3333333333333" style="1" customWidth="1"/>
-    <col min="7" max="7" width="16.2222222222222" style="1" customWidth="1"/>
+    <col min="1" max="6" width="19.3363636363636" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.2181818181818" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -3431,7 +3431,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="11" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -3451,7 +3451,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="12" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -3471,7 +3471,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="13" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -3491,7 +3491,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="14" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -3511,7 +3511,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="15" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -3541,10 +3541,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="6" width="19.3333333333333" style="1" customWidth="1"/>
-    <col min="7" max="7" width="16.2222222222222" style="1" customWidth="1"/>
+    <col min="1" max="6" width="19.3363636363636" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.2181818181818" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -3769,7 +3769,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="11" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -3789,7 +3789,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="12" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -3809,7 +3809,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="13" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -3829,7 +3829,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="14" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -3849,7 +3849,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="15" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -3879,10 +3879,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="5" width="19.3333333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.2222222222222" style="1" customWidth="1"/>
+    <col min="1" max="5" width="19.3363636363636" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.2181818181818" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -3940,7 +3940,7 @@
         <v>2</v>
       </c>
       <c r="E3" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>13</v>
@@ -3960,7 +3960,7 @@
         <v>3</v>
       </c>
       <c r="E4" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>13</v>
@@ -3980,7 +3980,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>13</v>
@@ -4000,7 +4000,7 @@
         <v>5</v>
       </c>
       <c r="E6" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>13</v>
@@ -4020,7 +4020,7 @@
         <v>6</v>
       </c>
       <c r="E7" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>13</v>
@@ -4070,9 +4070,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="5" width="19.3333333333333" style="1" customWidth="1"/>
+    <col min="1" max="5" width="19.3363636363636" style="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -4093,7 +4093,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="28.8" spans="1:5">
+    <row r="2" s="1" customFormat="1" ht="28" spans="1:5">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -4118,10 +4118,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="5" width="19.3333333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.2222222222222" style="1" customWidth="1"/>
+    <col min="1" max="5" width="19.3363636363636" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.2181818181818" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -4212,10 +4212,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="6" width="19.3333333333333" style="1" customWidth="1"/>
-    <col min="7" max="7" width="16.2222222222222" style="1" customWidth="1"/>
+    <col min="1" max="6" width="19.3363636363636" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.2181818181818" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -4440,7 +4440,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="11" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -4460,7 +4460,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="12" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -4480,7 +4480,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="13" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -4500,7 +4500,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="14" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -4520,7 +4520,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="15" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -4550,10 +4550,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="5" width="19.3333333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.2222222222222" style="1" customWidth="1"/>
+    <col min="1" max="5" width="19.3363636363636" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.2181818181818" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -4614,7 +4614,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="4" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -4641,10 +4641,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="6" width="19.3333333333333" style="1" customWidth="1"/>
-    <col min="7" max="7" width="16.2222222222222" style="1" customWidth="1"/>
+    <col min="1" max="6" width="19.3363636363636" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.2181818181818" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -4869,7 +4869,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="43.2" spans="1:7">
+    <row r="11" s="1" customFormat="1" ht="42" spans="1:7">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -4889,7 +4889,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="43.2" spans="1:7">
+    <row r="12" s="1" customFormat="1" ht="42" spans="1:7">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -4909,7 +4909,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="43.2" spans="1:7">
+    <row r="13" s="1" customFormat="1" ht="42" spans="1:7">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -4929,7 +4929,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="43.2" spans="1:7">
+    <row r="14" s="1" customFormat="1" ht="42" spans="1:7">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -4949,7 +4949,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="43.2" spans="1:7">
+    <row r="15" s="1" customFormat="1" ht="42" spans="1:7">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -4979,10 +4979,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="6" width="19.3333333333333" style="1" customWidth="1"/>
-    <col min="7" max="7" width="16.2222222222222" style="1" customWidth="1"/>
+    <col min="1" max="6" width="19.3363636363636" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.2181818181818" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -5207,7 +5207,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="11" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -5227,7 +5227,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="12" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -5247,7 +5247,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="13" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -5267,7 +5267,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="14" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -5287,7 +5287,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="15" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -5317,12 +5317,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="3" width="19.3333333333333" style="1" customWidth="1"/>
-    <col min="4" max="4" width="24.1111111111111" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.3333333333333" style="1" customWidth="1"/>
-    <col min="6" max="8" width="16.2222222222222" style="1" customWidth="1"/>
+    <col min="1" max="3" width="19.3363636363636" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.1090909090909" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.3363636363636" style="1" customWidth="1"/>
+    <col min="6" max="8" width="16.2181818181818" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -5378,7 +5378,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="3" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -5404,7 +5404,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="4" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -5430,7 +5430,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="5" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -5456,7 +5456,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="6" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -5482,7 +5482,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="7" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -5502,7 +5502,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="8" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -5522,7 +5522,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="9" s="1" customFormat="1" ht="42" spans="1:8">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -5555,10 +5555,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="6" width="19.3333333333333" style="1" customWidth="1"/>
-    <col min="7" max="7" width="16.2222222222222" style="1" customWidth="1"/>
+    <col min="1" max="6" width="19.3363636363636" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.2181818181818" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -5783,7 +5783,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="11" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -5803,7 +5803,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="12" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -5823,7 +5823,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="13" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -5843,7 +5843,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="14" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -5863,7 +5863,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="15" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -5893,10 +5893,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="6" width="19.3333333333333" style="1" customWidth="1"/>
-    <col min="7" max="7" width="16.2222222222222" style="1" customWidth="1"/>
+    <col min="1" max="6" width="19.3363636363636" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.2181818181818" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -6121,7 +6121,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="11" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -6141,7 +6141,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="12" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -6161,7 +6161,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="13" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -6181,7 +6181,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="14" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -6201,7 +6201,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="15" s="1" customFormat="1" ht="28" spans="1:7">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -6231,15 +6231,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="3" width="19.3333333333333" style="1" customWidth="1"/>
-    <col min="4" max="4" width="25.7777777777778" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.3333333333333" style="1" customWidth="1"/>
+    <col min="1" max="3" width="19.3363636363636" style="1" customWidth="1"/>
+    <col min="4" max="4" width="25.7818181818182" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.3363636363636" style="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6259,7 +6259,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="2" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -6279,7 +6279,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="3" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -6299,7 +6299,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="4" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -6329,13 +6329,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="5" width="19.3333333333333" style="1" customWidth="1"/>
+    <col min="1" max="5" width="19.3363636363636" style="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6355,7 +6355,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="2" s="1" customFormat="1" ht="28" spans="1:6">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -6375,7 +6375,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" ht="28.8" spans="1:6">
+    <row r="3" ht="28" spans="1:6">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -6395,7 +6395,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" ht="28.8" spans="1:6">
+    <row r="4" ht="28" spans="1:6">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -6415,7 +6415,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" ht="28.8" spans="1:6">
+    <row r="5" ht="28" spans="1:6">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -6435,7 +6435,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" ht="28.8" spans="1:6">
+    <row r="6" ht="28" spans="1:6">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -6455,7 +6455,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" ht="28.8" spans="1:6">
+    <row r="7" ht="28" spans="1:6">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -6475,7 +6475,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" ht="28.8" spans="1:6">
+    <row r="8" ht="28" spans="1:6">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -6492,7 +6492,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" ht="28.8" spans="1:6">
+    <row r="9" ht="28" spans="1:6">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -6520,10 +6520,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="5" width="19.3333333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.2222222222222" style="1" customWidth="1"/>
+    <col min="1" max="5" width="19.3363636363636" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.2181818181818" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -6711,10 +6711,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="5" width="19.3333333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.2222222222222" style="1" customWidth="1"/>
+    <col min="1" max="5" width="19.3363636363636" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.2181818181818" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -6902,10 +6902,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="5" width="19.3333333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.2222222222222" style="1" customWidth="1"/>
+    <col min="1" max="5" width="19.3363636363636" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.2181818181818" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -7093,10 +7093,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="5" width="19.3333333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.2222222222222" style="1" customWidth="1"/>
+    <col min="1" max="5" width="19.3363636363636" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.2181818181818" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -7284,9 +7284,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="5" width="19.3333333333333" style="1" customWidth="1"/>
+    <col min="1" max="5" width="19.3363636363636" style="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -7331,10 +7331,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="5" width="19.3333333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.2222222222222" style="1" customWidth="1"/>
+    <col min="1" max="5" width="19.3363636363636" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.2181818181818" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
